--- a/objects/recent_any_cancer.xlsx
+++ b/objects/recent_any_cancer.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t xml:space="preserve">model</t>
   </si>
@@ -20,6 +20,9 @@
     <t xml:space="preserve">term</t>
   </si>
   <si>
+    <t xml:space="preserve">Severe COVID</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hospitalized</t>
   </si>
   <si>
@@ -35,55 +38,67 @@
     <t xml:space="preserve">1</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31 (2.11, 2.54)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92 (1.62, 2.27)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91 (3.27, 4.68)</t>
+    <t xml:space="preserve">2.50 (2.30, 2.72)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31 (2.12, 2.52)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93 (1.64, 2.27)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96 (3.34, 4.69)</t>
   </si>
   <si>
     <t xml:space="preserve">unadjusted_firth</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92 (3.27, 4.68)</t>
+    <t xml:space="preserve">3.96 (3.34, 4.68)</t>
   </si>
   <si>
     <t xml:space="preserve">adjustment1</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48 (1.34, 1.63)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22 (1.02, 1.46)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80 (1.49, 2.17)</t>
+    <t xml:space="preserve">1.55 (1.42, 1.69)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49 (1.36, 1.63)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23 (1.04, 1.46)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82 (1.53, 2.17)</t>
   </si>
   <si>
     <t xml:space="preserve">adjustment2</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51 (1.36, 1.68)</t>
+    <t xml:space="preserve">1.54 (1.39, 1.69)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50 (1.35, 1.65)</t>
   </si>
   <si>
     <t xml:space="preserve">1.22 (1.01, 1.47)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74 (1.42, 2.13)</t>
+    <t xml:space="preserve">1.66 (1.37, 2.01)</t>
   </si>
   <si>
     <t xml:space="preserve">adjustment3</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64 (1.47, 1.84)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59 (1.29, 1.95)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89 (1.52, 2.34)</t>
+    <t xml:space="preserve">1.63 (1.47, 1.80)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60 (1.44, 1.78)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58 (1.29, 1.92)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77 (1.44, 2.17)</t>
   </si>
 </sst>
 </file>
@@ -428,90 +443,108 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
+      <c r="F3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>17</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="F5" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="F6" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/objects/recent_any_cancer.xlsx
+++ b/objects/recent_any_cancer.xlsx
@@ -59,10 +59,10 @@
     <t xml:space="preserve">adjustment1</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55 (1.42, 1.69)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49 (1.36, 1.63)</t>
+    <t xml:space="preserve">1.56 (1.43, 1.70)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49 (1.36, 1.64)</t>
   </si>
   <si>
     <t xml:space="preserve">1.23 (1.04, 1.46)</t>
@@ -74,10 +74,10 @@
     <t xml:space="preserve">adjustment2</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54 (1.39, 1.69)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50 (1.35, 1.65)</t>
+    <t xml:space="preserve">1.54 (1.40, 1.69)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50 (1.36, 1.66)</t>
   </si>
   <si>
     <t xml:space="preserve">1.22 (1.01, 1.47)</t>
